--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.65984</v>
+        <v>17.07667</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13953</v>
+        <v>16.57352</v>
       </c>
       <c r="E2" t="n">
-        <v>16.34912</v>
+        <v>16.66407</v>
       </c>
       <c r="F2" t="n">
-        <v>22.19415</v>
+        <v>42.03467</v>
       </c>
       <c r="G2" t="n">
-        <v>34.1709</v>
+        <v>0.04973</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.83687</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.16857</v>
+        <v>16.82289</v>
       </c>
       <c r="D3" t="n">
-        <v>16.29181</v>
+        <v>16.74664</v>
       </c>
       <c r="E3" t="n">
-        <v>16.07619</v>
+        <v>16.79049</v>
       </c>
       <c r="F3" t="n">
-        <v>21.95599</v>
+        <v>42.09194</v>
       </c>
       <c r="G3" t="n">
-        <v>34.0177</v>
+        <v>0.04985</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.83372</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.51176</v>
+        <v>16.90694</v>
       </c>
       <c r="D4" t="n">
-        <v>16.03262</v>
+        <v>16.67673</v>
       </c>
       <c r="E4" t="n">
-        <v>16.30569</v>
+        <v>16.72991</v>
       </c>
       <c r="F4" t="n">
-        <v>21.43611</v>
+        <v>42.39002</v>
       </c>
       <c r="G4" t="n">
-        <v>34.40119</v>
+        <v>0.05025</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.80362</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.76524</v>
+        <v>16.93123</v>
       </c>
       <c r="D5" t="n">
-        <v>16.15795</v>
+        <v>16.37317</v>
       </c>
       <c r="E5" t="n">
-        <v>16.27281</v>
+        <v>16.47404</v>
       </c>
       <c r="F5" t="n">
-        <v>21.14004</v>
+        <v>42.49517</v>
       </c>
       <c r="G5" t="n">
-        <v>34.51717</v>
+        <v>0.05047</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.79756</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.58919</v>
+        <v>16.98378</v>
       </c>
       <c r="D6" t="n">
-        <v>15.69896</v>
+        <v>16.49444</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41194</v>
+        <v>16.94504</v>
       </c>
       <c r="F6" t="n">
-        <v>21.72803</v>
+        <v>42.4978</v>
       </c>
       <c r="G6" t="n">
-        <v>34.26454</v>
+        <v>0.05141</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83562</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88638</v>
+        <v>16.50032</v>
       </c>
       <c r="D7" t="n">
-        <v>16.14595</v>
+        <v>16.46545</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50136</v>
+        <v>16.46961</v>
       </c>
       <c r="F7" t="n">
-        <v>21.57725</v>
+        <v>42.89418</v>
       </c>
       <c r="G7" t="n">
-        <v>33.87634</v>
+        <v>0.05022</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.75604</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.51879</v>
+        <v>16.96314</v>
       </c>
       <c r="D8" t="n">
-        <v>16.2708</v>
+        <v>16.68065</v>
       </c>
       <c r="E8" t="n">
-        <v>16.38048</v>
+        <v>16.71465</v>
       </c>
       <c r="F8" t="n">
-        <v>21.87571</v>
+        <v>43.19316</v>
       </c>
       <c r="G8" t="n">
-        <v>33.67897</v>
+        <v>0.05082</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.81944</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.67843</v>
+        <v>16.76816</v>
       </c>
       <c r="D9" t="n">
-        <v>16.45474</v>
+        <v>16.35695</v>
       </c>
       <c r="E9" t="n">
-        <v>16.3189</v>
+        <v>16.75724</v>
       </c>
       <c r="F9" t="n">
-        <v>22.37671</v>
+        <v>41.90233</v>
       </c>
       <c r="G9" t="n">
-        <v>35.00386</v>
+        <v>0.05059</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.82352</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.91727</v>
+        <v>16.85805</v>
       </c>
       <c r="D10" t="n">
-        <v>15.96299</v>
+        <v>16.55946</v>
       </c>
       <c r="E10" t="n">
-        <v>16.66126</v>
+        <v>16.74695</v>
       </c>
       <c r="F10" t="n">
-        <v>21.91801</v>
+        <v>43.11922</v>
       </c>
       <c r="G10" t="n">
-        <v>34.37278</v>
+        <v>0.05067</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8792</v>
       </c>
     </row>
     <row r="11">
@@ -686,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.78748</v>
+        <v>16.798</v>
       </c>
       <c r="D12" t="n">
-        <v>16.28678</v>
+        <v>16.53642</v>
       </c>
       <c r="E12" t="n">
-        <v>16.43644</v>
+        <v>16.75759</v>
       </c>
       <c r="F12" t="n">
-        <v>42.15099</v>
+        <v>41.56488</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0507</v>
+        <v>0.05037</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82363</v>
+        <v>1.83514</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.5803</v>
+        <v>17.21848</v>
       </c>
       <c r="D13" t="n">
-        <v>16.2189</v>
+        <v>16.7978</v>
       </c>
       <c r="E13" t="n">
-        <v>16.73544</v>
+        <v>16.91492</v>
       </c>
       <c r="F13" t="n">
-        <v>42.65767</v>
+        <v>42.68105</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05112</v>
+        <v>0.051</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82166</v>
+        <v>1.84507</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.00137</v>
+        <v>16.87937</v>
       </c>
       <c r="D14" t="n">
-        <v>16.39646</v>
+        <v>16.67679</v>
       </c>
       <c r="E14" t="n">
-        <v>16.97567</v>
+        <v>16.82657</v>
       </c>
       <c r="F14" t="n">
-        <v>42.12729</v>
+        <v>41.78687</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05077</v>
+        <v>0.05051</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81762</v>
+        <v>1.84176</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.05163</v>
+        <v>16.88117</v>
       </c>
       <c r="D15" t="n">
-        <v>16.49208</v>
+        <v>16.76754</v>
       </c>
       <c r="E15" t="n">
-        <v>16.60109</v>
+        <v>16.86151</v>
       </c>
       <c r="F15" t="n">
-        <v>42.22655</v>
+        <v>42.53731</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05068</v>
+        <v>0.05139</v>
       </c>
       <c r="H15" t="n">
-        <v>1.80858</v>
+        <v>1.83053</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.93149</v>
+        <v>16.84732</v>
       </c>
       <c r="D16" t="n">
-        <v>16.54699</v>
+        <v>16.58328</v>
       </c>
       <c r="E16" t="n">
-        <v>16.74321</v>
+        <v>16.62511</v>
       </c>
       <c r="F16" t="n">
-        <v>42.55544</v>
+        <v>42.66027</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05053</v>
+        <v>0.05177</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8314</v>
+        <v>1.83464</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.56295</v>
+        <v>17.00145</v>
       </c>
       <c r="D17" t="n">
-        <v>16.33165</v>
+        <v>16.69993</v>
       </c>
       <c r="E17" t="n">
-        <v>16.5683</v>
+        <v>16.84421</v>
       </c>
       <c r="F17" t="n">
-        <v>42.87859</v>
+        <v>42.4646</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05197</v>
+        <v>0.05097</v>
       </c>
       <c r="H17" t="n">
-        <v>1.84216</v>
+        <v>1.82065</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.58159</v>
+        <v>16.76952</v>
       </c>
       <c r="D18" t="n">
-        <v>16.37296</v>
+        <v>16.5925</v>
       </c>
       <c r="E18" t="n">
-        <v>16.85833</v>
+        <v>16.73125</v>
       </c>
       <c r="F18" t="n">
-        <v>42.79007</v>
+        <v>42.75291</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04967</v>
+        <v>0.05092</v>
       </c>
       <c r="H18" t="n">
-        <v>1.81808</v>
+        <v>1.78517</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.79116</v>
+        <v>17.1116</v>
       </c>
       <c r="D19" t="n">
-        <v>16.83023</v>
+        <v>16.63078</v>
       </c>
       <c r="E19" t="n">
-        <v>16.57511</v>
+        <v>16.8019</v>
       </c>
       <c r="F19" t="n">
-        <v>42.09797</v>
+        <v>42.85036</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05227</v>
+        <v>0.04987</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84984</v>
+        <v>1.81876</v>
       </c>
     </row>
     <row r="20">
@@ -890,22 +922,948 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.85007</v>
+        <v>16.83362</v>
       </c>
       <c r="D20" t="n">
-        <v>16.57335</v>
+        <v>16.78881</v>
       </c>
       <c r="E20" t="n">
-        <v>16.74509</v>
+        <v>16.81189</v>
       </c>
       <c r="F20" t="n">
-        <v>43.60888</v>
+        <v>42.35902</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05035</v>
+        <v>0.05038</v>
       </c>
       <c r="H20" t="n">
-        <v>1.81059</v>
+        <v>1.81305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.69126</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.37902</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.63876</v>
+      </c>
+      <c r="F22" t="n">
+        <v>261.5093</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.85158</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.60069</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.76284</v>
+      </c>
+      <c r="F23" t="n">
+        <v>257.31019</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.63032</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.22548</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.60925</v>
+      </c>
+      <c r="F24" t="n">
+        <v>258.4951</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.83772</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.52512</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.60866</v>
+      </c>
+      <c r="F25" t="n">
+        <v>256.03202</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16.11855</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.37985</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.51558</v>
+      </c>
+      <c r="F26" t="n">
+        <v>254.42786</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.67883</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.41432</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.46961</v>
+      </c>
+      <c r="F27" t="n">
+        <v>254.57643</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.76501</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.61987</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.70279</v>
+      </c>
+      <c r="F28" t="n">
+        <v>255.6665</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.90103</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.6697</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.7009</v>
+      </c>
+      <c r="F29" t="n">
+        <v>253.11348</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.52608</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.39726</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.48833</v>
+      </c>
+      <c r="F30" t="n">
+        <v>256.25693</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.51405</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.82531</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.47708</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.59099</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33.96106</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.87991</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.08339</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.18835</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.44019</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.4813</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.88948</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.16876</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.6928</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.63108</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.33983</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.15215</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.9846</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.54866</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.39928</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.68233</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.60044</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.04291</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.57186</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.72974</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33.87204</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.72464</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.80866</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.57015</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.50384</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.15932</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.83769</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.03463</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.17466</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.21635</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.39386</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.83197</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.91783</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.71586</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.73308</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.15531</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.71964</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.80361</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.52919</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.48939</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.94275</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.41372</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.75761</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.27471</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.49622</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.80583</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.86487</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.9088</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.39695</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.81847</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.27762</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.67787</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.04131</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.34555</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.74986</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.91364</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.75963</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.04052</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.118</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.8218</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.61725</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.12565</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.27209</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.92826</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.18216</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.83525</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.88401</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.70523</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.96772</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.31339</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.75359</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.98889</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.20354</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.06841</v>
+      </c>
+      <c r="G48" t="n">
+        <v>33.92722</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.56828</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.12414</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.36095</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.43888</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.81238</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.63852</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.96977</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.63128</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.42603</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.38813</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.59865</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.11226</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.5972499999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.12195</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.59617</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.12364</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.12419</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.59065</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.13643</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.07965</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61328</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.12947</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60968</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.10688</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.59659</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.12289</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61775</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11612</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.60634</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.14036</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.59196</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.12307</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.61243</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.12553</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60146</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.10893</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.61761</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.0994</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.60534</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.11109</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5923</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.09647</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.6009100000000001</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.1343</v>
       </c>
     </row>
   </sheetData>
